--- a/预测水位/OutputData/水地1.xlsx
+++ b/预测水位/OutputData/水地1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -686,12 +686,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1046,11 +1040,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2161"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B2185"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="32.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="38.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="32.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="38.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -17922,88 +17916,271 @@
       <c r="B2149" s="6"/>
     </row>
     <row r="2150" spans="1:2">
-      <c r="A2150" s="7">
+      <c r="A2150" s="5">
         <v>45837</v>
       </c>
-      <c r="B2150" s="8">
+      <c r="B2150" s="6">
         <v>887.547</v>
       </c>
     </row>
     <row r="2151" spans="1:2">
-      <c r="A2151" s="7">
+      <c r="A2151" s="5">
         <v>45837.0833333333</v>
       </c>
-      <c r="B2151" s="8"/>
+      <c r="B2151" s="6"/>
     </row>
     <row r="2152" spans="1:2">
-      <c r="A2152" s="7">
+      <c r="A2152" s="5">
         <v>45837.1666666667</v>
       </c>
-      <c r="B2152" s="8">
+      <c r="B2152" s="6">
         <v>887.693</v>
       </c>
     </row>
     <row r="2153" spans="1:2">
-      <c r="A2153" s="7">
+      <c r="A2153" s="5">
         <v>45837.25</v>
       </c>
-      <c r="B2153" s="8"/>
+      <c r="B2153" s="6"/>
     </row>
     <row r="2154" spans="1:2">
-      <c r="A2154" s="7">
+      <c r="A2154" s="5">
         <v>45837.3333333333</v>
       </c>
-      <c r="B2154" s="8">
+      <c r="B2154" s="6">
         <v>887.736</v>
       </c>
     </row>
     <row r="2155" spans="1:2">
-      <c r="A2155" s="7">
+      <c r="A2155" s="5">
         <v>45837.4166666667</v>
       </c>
-      <c r="B2155" s="8"/>
+      <c r="B2155" s="6"/>
     </row>
     <row r="2156" spans="1:2">
-      <c r="A2156" s="7">
+      <c r="A2156" s="5">
         <v>45837.5</v>
       </c>
-      <c r="B2156" s="8">
+      <c r="B2156" s="6">
         <v>887.699</v>
       </c>
     </row>
     <row r="2157" spans="1:2">
-      <c r="A2157" s="7">
+      <c r="A2157" s="5">
         <v>45837.5833333333</v>
       </c>
-      <c r="B2157" s="8"/>
+      <c r="B2157" s="6"/>
     </row>
     <row r="2158" spans="1:2">
-      <c r="A2158" s="7">
+      <c r="A2158" s="5">
         <v>45837.6666666667</v>
       </c>
-      <c r="B2158" s="8">
+      <c r="B2158" s="6">
         <v>887.543</v>
       </c>
     </row>
     <row r="2159" spans="1:2">
-      <c r="A2159" s="7">
+      <c r="A2159" s="5">
         <v>45837.75</v>
       </c>
-      <c r="B2159" s="8"/>
+      <c r="B2159" s="6"/>
     </row>
     <row r="2160" spans="1:2">
-      <c r="A2160" s="7">
+      <c r="A2160" s="5">
         <v>45837.8333333333</v>
       </c>
-      <c r="B2160" s="8">
+      <c r="B2160" s="6">
         <v>887.452</v>
       </c>
     </row>
     <row r="2161" spans="1:2">
-      <c r="A2161" s="7">
+      <c r="A2161" s="5">
         <v>45837.9166666667</v>
       </c>
-      <c r="B2161" s="8"/>
+      <c r="B2161" s="6"/>
+    </row>
+    <row r="2162" spans="1:2">
+      <c r="A2162" s="5">
+        <v>45838</v>
+      </c>
+      <c r="B2162" s="6">
+        <v>887.348</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:2">
+      <c r="A2163" s="5">
+        <v>45838.0833333333</v>
+      </c>
+      <c r="B2163" s="6"/>
+    </row>
+    <row r="2164" spans="1:2">
+      <c r="A2164" s="5">
+        <v>45838.1666666667</v>
+      </c>
+      <c r="B2164" s="6">
+        <v>887.287</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:2">
+      <c r="A2165" s="5">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" s="6"/>
+    </row>
+    <row r="2166" spans="1:2">
+      <c r="A2166" s="5">
+        <v>45838.3333333333</v>
+      </c>
+      <c r="B2166" s="6">
+        <v>887.236</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:2">
+      <c r="A2167" s="5">
+        <v>45838.4166666667</v>
+      </c>
+      <c r="B2167" s="6"/>
+    </row>
+    <row r="2168" spans="1:2">
+      <c r="A2168" s="5">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" s="6">
+        <v>887.163</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:2">
+      <c r="A2169" s="5">
+        <v>45838.5833333333</v>
+      </c>
+      <c r="B2169" s="6"/>
+    </row>
+    <row r="2170" spans="1:2">
+      <c r="A2170" s="5">
+        <v>45838.6666666667</v>
+      </c>
+      <c r="B2170" s="6">
+        <v>887.114</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:2">
+      <c r="A2171" s="5">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" s="6"/>
+    </row>
+    <row r="2172" spans="1:2">
+      <c r="A2172" s="5">
+        <v>45838.8333333333</v>
+      </c>
+      <c r="B2172" s="6">
+        <v>887.044</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:2">
+      <c r="A2173" s="5">
+        <v>45838.9166666667</v>
+      </c>
+      <c r="B2173" s="6"/>
+    </row>
+    <row r="2174" spans="1:2">
+      <c r="A2174" s="5">
+        <v>45839</v>
+      </c>
+      <c r="B2174" s="6">
+        <v>886.987</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:2">
+      <c r="A2175" s="5">
+        <v>45839.0833333333</v>
+      </c>
+      <c r="B2175" s="6">
+        <f t="shared" ref="B2175:B2179" si="1">B2174/2+B2176/2</f>
+        <v>886.979</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:2">
+      <c r="A2176" s="5">
+        <v>45839.1666666667</v>
+      </c>
+      <c r="B2176" s="6">
+        <v>886.971</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:2">
+      <c r="A2177" s="5">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" s="6">
+        <f t="shared" si="1"/>
+        <v>886.953</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:2">
+      <c r="A2178" s="5">
+        <v>45839.3333333333</v>
+      </c>
+      <c r="B2178" s="6">
+        <v>886.935</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:2">
+      <c r="A2179" s="5">
+        <v>45839.4166666667</v>
+      </c>
+      <c r="B2179" s="6">
+        <f t="shared" si="1"/>
+        <v>886.9245</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:2">
+      <c r="A2180" s="5">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" s="6">
+        <v>886.914</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:2">
+      <c r="A2181" s="5">
+        <v>45839.5833333333</v>
+      </c>
+      <c r="B2181" s="6">
+        <f t="shared" ref="B2181:B2185" si="2">B2180/2+B2182/2</f>
+        <v>886.9025</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:2">
+      <c r="A2182" s="5">
+        <v>45839.6666666667</v>
+      </c>
+      <c r="B2182" s="6">
+        <v>886.891</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:2">
+      <c r="A2183" s="5">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" s="6">
+        <f t="shared" si="2"/>
+        <v>886.873</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:2">
+      <c r="A2184" s="5">
+        <v>45839.8333333333</v>
+      </c>
+      <c r="B2184" s="6">
+        <v>886.855</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:2">
+      <c r="A2185" s="5">
+        <v>45839.9166666667</v>
+      </c>
+      <c r="B2185" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
